--- a/قائمة الوحدات الخاصة بالفوج20252026/قائمة_جهة_نابل_فوج_قرمبالية_المدينة_وحدة_الكروان.xlsx
+++ b/قائمة الوحدات الخاصة بالفوج20252026/قائمة_جهة_نابل_فوج_قرمبالية_المدينة_وحدة_الكروان.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
   <si>
     <t>المعرف</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>المختار</t>
+  </si>
+  <si>
+    <t>code_unite</t>
+  </si>
+  <si>
+    <t>CHBL</t>
   </si>
 </sst>
 </file>
@@ -472,6 +478,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -498,8 +507,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>26</v>
       </c>
       <c r="B2">
         <v>900002913</v>
@@ -527,8 +536,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>26</v>
       </c>
       <c r="B3">
         <v>900009452</v>
@@ -556,8 +565,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
+      <c r="A4" t="s">
+        <v>26</v>
       </c>
       <c r="B4">
         <v>900010758</v>
@@ -585,8 +594,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
+      <c r="A5" t="s">
+        <v>26</v>
       </c>
       <c r="B5">
         <v>900013352</v>
@@ -614,8 +623,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3</v>
+      <c r="A6" t="s">
+        <v>26</v>
       </c>
       <c r="B6">
         <v>900008353</v>
@@ -643,8 +652,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>4</v>
+      <c r="A7" t="s">
+        <v>26</v>
       </c>
       <c r="B7">
         <v>900013102</v>
@@ -674,7 +683,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A3:H3 A4:I7 A2:H2" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:I1 B3:H3 B7:I7 B2:H2 B4:I4 B5:I5 B6:I6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>